--- a/public/sample_questions_std10.xlsx
+++ b/public/sample_questions_std10.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N11"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -406,11 +406,13 @@
     <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="50.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="50.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +455,9 @@
       <c r="M1" t="str">
         <v>Image</v>
       </c>
+      <c r="N1" t="str">
+        <v>Difficulty</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -494,6 +499,9 @@
       <c r="M2" t="str">
         <v>water_question.jpg</v>
       </c>
+      <c r="N2" t="str">
+        <v>easy</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -535,6 +543,9 @@
       <c r="M3" t="str">
         <v>mars_question.jpg</v>
       </c>
+      <c r="N3" t="str">
+        <v>easy</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -576,6 +587,9 @@
       <c r="M4" t="str">
         <v>capital_question.jpg</v>
       </c>
+      <c r="N4" t="str">
+        <v>medium</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -617,6 +631,9 @@
       <c r="M5" t="str">
         <v>book_question.jpg</v>
       </c>
+      <c r="N5" t="str">
+        <v>medium</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -658,6 +675,9 @@
       <c r="M6" t="str">
         <v>pi_question.jpg</v>
       </c>
+      <c r="N6" t="str">
+        <v>easy</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -699,6 +719,9 @@
       <c r="M7" t="str">
         <v>photosynthesis_question.jpg</v>
       </c>
+      <c r="N7" t="str">
+        <v>medium</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -740,6 +763,9 @@
       <c r="M8" t="str">
         <v>organ_question.jpg</v>
       </c>
+      <c r="N8" t="str">
+        <v>hard</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -781,6 +807,9 @@
       <c r="M9" t="str">
         <v>independence_question.jpg</v>
       </c>
+      <c r="N9" t="str">
+        <v>medium</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -822,6 +851,9 @@
       <c r="M10" t="str">
         <v>math_question.jpg</v>
       </c>
+      <c r="N10" t="str">
+        <v>easy</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -863,10 +895,13 @@
       <c r="M11" t="str">
         <v>river_question.jpg</v>
       </c>
+      <c r="N11" t="str">
+        <v>hard</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N11"/>
   </ignoredErrors>
 </worksheet>
 </file>